--- a/manuscript_material/source_data/Source_Data_Fig4.xlsx
+++ b/manuscript_material/source_data/Source_Data_Fig4.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="a_software_families" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="b_jaccard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="c_non_unanimous_triplicates" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="c_split_replicate_sets" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="d_divergence_mechanisms" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
@@ -427,32 +427,32 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>BixBench-Verified-50, Open-ended code</t>
+          <t>BixBench-Verified-50, Open-ended code condition</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>BixBench-Verified-50, Galaxy</t>
+          <t>BixBench-Verified-50, Galaxy condition</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>CompBioBench, Open-ended code</t>
+          <t>CompBioBench, Open-ended code condition</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>CompBioBench, Galaxy</t>
+          <t>CompBioBench, Galaxy condition</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>IWC, Open-ended code</t>
+          <t>IWC, Open-ended code condition</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>IWC, Galaxy</t>
+          <t>IWC, Galaxy condition</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>configuration</t>
+          <t>model_configuration</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>mean_pairwise_jaccard</t>
+          <t>galaxy_tool_set_similarity</t>
         </is>
       </c>
     </row>
@@ -1281,22 +1281,22 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>configuration</t>
+          <t>model_configuration</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>open_ended_code</t>
+          <t>split_sets_open_ended_code</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>galaxy</t>
+          <t>split_sets_galaxy</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>tasks_per_configuration</t>
+          <t>replicate_sets_per_condition</t>
         </is>
       </c>
     </row>
@@ -1590,17 +1590,17 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>environment</t>
+          <t>execution_condition</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>mechanism</t>
+          <t>divergence_mechanism</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>rejected_replicates</t>
+          <t>scored_incorrect_replicate_runs</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -1617,7 +1617,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1638,7 +1638,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1659,7 +1659,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1680,7 +1680,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1701,7 +1701,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1722,7 +1722,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1743,7 +1743,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1764,7 +1764,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1806,7 +1806,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1827,7 +1827,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1848,7 +1848,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">

--- a/manuscript_material/source_data/Source_Data_Fig4.xlsx
+++ b/manuscript_material/source_data/Source_Data_Fig4.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="a_software_families" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="b_jaccard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="c_split_replicate_sets" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="d_divergence_mechanisms" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="a_repeatability_categories" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="b_distinct_answers" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="c_divergence_mechanisms" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="d_run_level_versus_unanimous" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,636 +416,629 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>model_configuration</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>BixBench-Verified-50, Open-ended code condition</t>
+          <t>execution_condition</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>BixBench-Verified-50, Galaxy condition</t>
+          <t>repeatability_category</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>CompBioBench, Open-ended code condition</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>CompBioBench, Galaxy condition</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>IWC, Open-ended code condition</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>IWC, Galaxy condition</t>
+          <t>replicate_sets</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>phykit</t>
+          <t>GPT-5.5</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54/450</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>60/428</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0/900</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0/898</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0/90</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0/89</t>
-        </is>
+          <t>3/3 scored correct</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DESeq2 / PyDESeq2</t>
+          <t>GPT-5.5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>78/450</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>29/428</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0/900</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1/898</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>18/90</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>10/89</t>
-        </is>
+          <t>Split (1–2/3)</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>gseapy</t>
+          <t>GPT-5.5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>36/450</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>24/428</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0/900</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>5/898</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0/90</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0/89</t>
-        </is>
+          <t>0/3 scored correct</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>samtools</t>
+          <t>GPT-5.5</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17/450</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>9/428</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>252/900</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>92/898</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>36/90</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>11/89</t>
-        </is>
+          <t>3/3 scored correct</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>bcftools</t>
+          <t>GPT-5.5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10/450</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>9/428</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>105/900</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>41/898</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>7/90</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0/89</t>
-        </is>
+          <t>Split (1–2/3)</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>bedtools</t>
+          <t>GPT-5.5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0/450</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0/428</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>129/900</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>100/898</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>12/90</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2/89</t>
-        </is>
+          <t>0/3 scored correct</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>anndata</t>
+          <t>GPT-5.6 Sol</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10/450</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0/428</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>89/900</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>64/898</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>9/90</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>6/89</t>
-        </is>
+          <t>3/3 scored correct</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>41</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>scanpy</t>
+          <t>GPT-5.6 Sol</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3/450</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0/428</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>79/900</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>33/898</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>9/90</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0/89</t>
-        </is>
+          <t>Split (1–2/3)</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>datamash</t>
+          <t>GPT-5.6 Sol</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0/450</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>33/428</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0/900</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>82/898</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>1/90</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0/89</t>
-        </is>
+          <t>0/3 scored correct</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>bwa</t>
+          <t>GPT-5.6 Sol</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>9/450</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>9/428</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>126/900</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>52/898</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>23/90</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>4/89</t>
-        </is>
+          <t>3/3 scored correct</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>fastp</t>
+          <t>GPT-5.6 Sol</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0/450</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0/428</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>44/900</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0/898</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>25/90</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>18/89</t>
-        </is>
+          <t>Split (1–2/3)</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>bowtie2</t>
+          <t>GPT-5.6 Sol</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1/450</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0/428</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>123/900</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>24/898</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>20/90</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>18/89</t>
-        </is>
+          <t>0/3 scored correct</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>minimap2</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5/450</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0/428</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>169/900</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>21/898</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>24/90</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>1/89</t>
-        </is>
+          <t>3/3 scored correct</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MACS2 / MACS3</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0/450</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0/428</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>44/900</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>12/898</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>9/90</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>7/89</t>
-        </is>
+          <t>Split (1–2/3)</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>edgeR</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20/450</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2/428</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>0/900</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>2/898</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>13/90</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>9/89</t>
-        </is>
+          <t>0/3 scored correct</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>dada2</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0/450</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0/428</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>0/900</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0/898</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>9/90</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>8/89</t>
-        </is>
+          <t>3/3 scored correct</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>GPT-5.6 Luna</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Split (1–2/3)</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>GPT-5.6 Luna</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0/3 scored correct</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Codex)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3/3 scored correct</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Codex)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Split (1–2/3)</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Codex)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0/3 scored correct</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Codex)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>3/3 scored correct</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Codex)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Split (1–2/3)</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Codex)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0/3 scored correct</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Claude Code, superseded)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>3/3 scored correct</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Claude Code, superseded)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Split (1–2/3)</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Claude Code, superseded)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0/3 scored correct</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Claude Code, superseded)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>3/3 scored correct</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Claude Code, superseded)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Split (1–2/3)</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Claude Code, superseded)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0/3 scored correct</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1059,204 +1052,461 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>benchmark</t>
+          <t>model_configuration</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>model_configuration</t>
+          <t>execution_condition</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>galaxy_tool_set_similarity</t>
+          <t>distinct_answers</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>replicate_sets</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BixBench-Verified-50</t>
+          <t>GPT-5.5</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GPT-5.5</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.26</v>
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CompBioBench</t>
+          <t>GPT-5.5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GPT-5.5</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.089</v>
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IWC</t>
+          <t>GPT-5.5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GPT-5.5</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.72</v>
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BixBench-Verified-50</t>
+          <t>GPT-5.5</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.501</v>
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CompBioBench</t>
+          <t>GPT-5.5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.125</v>
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IWC</t>
+          <t>GPT-5.5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.547</v>
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BixBench-Verified-50</t>
+          <t>GPT-5.6 Sol</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.426</v>
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>89</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CompBioBench</t>
+          <t>GPT-5.6 Sol</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.19</v>
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IWC</t>
+          <t>GPT-5.6 Sol</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.576</v>
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BixBench-Verified-50</t>
+          <t>GPT-5.6 Sol</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Pro</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.625</v>
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>87</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CompBioBench</t>
+          <t>GPT-5.6 Sol</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Pro</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.203</v>
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IWC</t>
+          <t>GPT-5.6 Sol</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Pro</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.628</v>
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>GPT-5.6 Luna</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>GPT-5.6 Luna</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>GPT-5.6 Luna</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>GPT-5.6 Luna</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>GPT-5.6 Luna</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>GPT-5.6 Luna</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Codex)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Codex)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Codex)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Codex)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Codex)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Codex)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1270,307 +1520,286 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>benchmark</t>
+          <t>execution_condition</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>model_configuration</t>
+          <t>divergence_mechanism</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>split_sets_open_ended_code</t>
+          <t>scored_incorrect_replicate_runs</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>split_sets_galaxy</t>
+          <t>total</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>replicate_sets_per_condition</t>
+          <t>percent</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BixBench-Verified-50</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GPT-5.5</t>
+          <t>Domain convention or definition applied differently</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="E2" t="n">
-        <v>50</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BixBench-Verified-50</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol</t>
+          <t>Error in the final step (sorting, counting, units)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="E3" t="n">
-        <v>50</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BixBench-Verified-50</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>Hand-written method instead of the library method</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="E4" t="n">
-        <v>50</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BixBench-Verified-50</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Pro</t>
+          <t>Different software version installed</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="E5" t="n">
-        <v>50</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BixBench-Verified-50</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Pro (Claude Code, superseded)</t>
+          <t>No answer submitted</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="E6" t="n">
-        <v>50</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CompBioBench</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GPT-5.5</t>
+          <t>Answer retrieved from benchmark source files</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="E7" t="n">
-        <v>82</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CompBioBench</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol</t>
+          <t>Domain convention or definition applied differently</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="E8" t="n">
-        <v>82</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CompBioBench</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>Error in the final step (sorting, counting, units)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="E9" t="n">
-        <v>82</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CompBioBench</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Pro</t>
+          <t>Hand-written method instead of the library method</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E10" t="n">
-        <v>82</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IWC</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GPT-5.5</t>
+          <t>No answer submitted</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="E11" t="n">
-        <v>10</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IWC</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol</t>
+          <t>Galaxy interface trap (silent default, output semantics or job not dispatched)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="E12" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IWC</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>Answer retrieved from benchmark source files</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="E13" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>IWC</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>DeepSeek V4 Pro</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>3</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>10</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1584,286 +1813,244 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>model_configuration</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>execution_condition</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>divergence_mechanism</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>scored_incorrect_replicate_runs</t>
+          <t>run_level_accuracy</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>unanimous_accuracy</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>difference_pp</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Open-ended code condition</t>
+          <t>GPT-5.5</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Domain convention or definition applied differently</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>87.33</v>
       </c>
       <c r="D2" t="n">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="E2" t="n">
-        <v>24.4</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Open-ended code condition</t>
+          <t>GPT-5.5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Error in the final step (sorting, counting, units)</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>89.33</v>
       </c>
       <c r="D3" t="n">
-        <v>45</v>
+        <v>88</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Open-ended code condition</t>
+          <t>GPT-5.6 Sol</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hand-written method instead of the library method</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
+        <v>86.67</v>
       </c>
       <c r="D4" t="n">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="E4" t="n">
-        <v>51.1</v>
+        <v>-4.67</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Open-ended code condition</t>
+          <t>GPT-5.6 Sol</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Different software version installed</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>88.67</v>
       </c>
       <c r="D5" t="n">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="E5" t="n">
-        <v>15.6</v>
+        <v>-2.67</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Open-ended code condition</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>No answer submitted</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>86</v>
       </c>
       <c r="D6" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="E6" t="n">
-        <v>2.2</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Open-ended code condition</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Answer retrieved from benchmark source files</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>86</v>
       </c>
       <c r="D7" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="E7" t="n">
-        <v>4.4</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Galaxy condition</t>
+          <t>DeepSeek V4 Pro (Codex)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Domain convention or definition applied differently</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>80.67</v>
       </c>
       <c r="D8" t="n">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="E8" t="n">
-        <v>36.1</v>
+        <v>-6.67</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Galaxy condition</t>
+          <t>DeepSeek V4 Pro (Codex)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Error in the final step (sorting, counting, units)</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="D9" t="n">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="E9" t="n">
-        <v>16.7</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Galaxy condition</t>
+          <t>DeepSeek V4 Pro (Claude Code, superseded)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hand-written method instead of the library method</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>69.33</v>
       </c>
       <c r="D10" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="E10" t="n">
-        <v>13.9</v>
+        <v>-13.33</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Galaxy condition</t>
+          <t>DeepSeek V4 Pro (Claude Code, superseded)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>No answer submitted</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="D11" t="n">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="E11" t="n">
-        <v>8.300000000000001</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Galaxy condition</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Galaxy interface trap (silent default, output semantics or job not dispatched)</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>6</v>
-      </c>
-      <c r="D12" t="n">
-        <v>36</v>
-      </c>
-      <c r="E12" t="n">
-        <v>16.7</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Galaxy condition</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Answer retrieved from benchmark source files</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>3</v>
-      </c>
-      <c r="D13" t="n">
-        <v>36</v>
-      </c>
-      <c r="E13" t="n">
-        <v>8.300000000000001</v>
+        <v>-16</v>
       </c>
     </row>
   </sheetData>

--- a/manuscript_material/source_data/Source_Data_Fig4.xlsx
+++ b/manuscript_material/source_data/Source_Data_Fig4.xlsx
@@ -7,10 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="a_repeatability_categories" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="b_distinct_answers" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="c_divergence_mechanisms" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="d_run_level_versus_unanimous" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="a_iwc_split_replicate_sets" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="b_repeatability_categories" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="c_consensus_repeatability" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="d_divergence_mechanisms" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="e_run_level_versus_unanimous" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,26 +417,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>benchmark</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>model_configuration</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>execution_condition</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>repeatability_category</t>
-        </is>
-      </c>
       <c r="D1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
         <is>
           <t>replicate_sets</t>
         </is>
@@ -444,601 +450,601 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>IWC</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>GPT-5.5</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Open-ended code condition</t>
-        </is>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3/3 scored correct</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>43</v>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Range 0.05 or less</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>IWC</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>GPT-5.5</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Open-ended code condition</t>
-        </is>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Split (1–2/3)</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Split (range above 0.05)</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>IWC</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>GPT-5.5</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Open-ended code condition</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0/3 scored correct</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>6</v>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Not scored</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>IWC</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>GPT-5.5</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Galaxy condition</t>
-        </is>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3/3 scored correct</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>44</v>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Range 0.05 or less</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>IWC</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>GPT-5.5</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Galaxy condition</t>
-        </is>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Split (1–2/3)</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Split (range above 0.05)</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>IWC</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>GPT-5.5</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Galaxy condition</t>
-        </is>
-      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0/3 scored correct</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>5</v>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Not scored</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>IWC</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>GPT-5.6 Sol</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Open-ended code condition</t>
-        </is>
-      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3/3 scored correct</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>41</v>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Range 0.05 or less</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>IWC</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>GPT-5.6 Sol</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Open-ended code condition</t>
-        </is>
-      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Split (1–2/3)</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>4</v>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Split (range above 0.05)</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>IWC</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>GPT-5.6 Sol</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Open-ended code condition</t>
-        </is>
-      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0/3 scored correct</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>5</v>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Not scored</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>IWC</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>GPT-5.6 Sol</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Galaxy condition</t>
-        </is>
-      </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3/3 scored correct</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>43</v>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Range 0.05 or less</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>IWC</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>GPT-5.6 Sol</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Galaxy condition</t>
-        </is>
-      </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Split (1–2/3)</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>2</v>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Split (range above 0.05)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>IWC</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>GPT-5.6 Sol</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Galaxy condition</t>
-        </is>
-      </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0/3 scored correct</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>5</v>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Not scored</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>IWC</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>GPT-5.6 Luna</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Open-ended code condition</t>
-        </is>
-      </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3/3 scored correct</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>38</v>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Range 0.05 or less</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>IWC</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>GPT-5.6 Luna</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Open-ended code condition</t>
-        </is>
-      </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Split (1–2/3)</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>8</v>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Split (range above 0.05)</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>IWC</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>GPT-5.6 Luna</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Open-ended code condition</t>
-        </is>
-      </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0/3 scored correct</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>4</v>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Not scored</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>IWC</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>GPT-5.6 Luna</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Galaxy condition</t>
-        </is>
-      </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3/3 scored correct</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>40</v>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Range 0.05 or less</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>IWC</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>GPT-5.6 Luna</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Galaxy condition</t>
-        </is>
-      </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Split (1–2/3)</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>5</v>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Split (range above 0.05)</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>IWC</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>GPT-5.6 Luna</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Galaxy condition</t>
-        </is>
-      </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0/3 scored correct</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>5</v>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Not scored</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>IWC</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>DeepSeek V4 Pro (Codex)</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Open-ended code condition</t>
-        </is>
-      </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3/3 scored correct</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>37</v>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Range 0.05 or less</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>IWC</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>DeepSeek V4 Pro (Codex)</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Open-ended code condition</t>
-        </is>
-      </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Split (1–2/3)</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>6</v>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Split (range above 0.05)</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>IWC</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>DeepSeek V4 Pro (Codex)</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Open-ended code condition</t>
-        </is>
-      </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0/3 scored correct</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>7</v>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Not scored</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>IWC</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>DeepSeek V4 Pro (Codex)</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Galaxy condition</t>
-        </is>
-      </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3/3 scored correct</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>38</v>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Range 0.05 or less</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>IWC</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>DeepSeek V4 Pro (Codex)</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Galaxy condition</t>
-        </is>
-      </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Split (1–2/3)</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>7</v>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Split (range above 0.05)</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>IWC</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>DeepSeek V4 Pro (Codex)</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Galaxy condition</t>
-        </is>
-      </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0/3 scored correct</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>DeepSeek V4 Pro (Claude Code, superseded)</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Open-ended code condition</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>3/3 scored correct</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>DeepSeek V4 Pro (Claude Code, superseded)</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Open-ended code condition</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Split (1–2/3)</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>DeepSeek V4 Pro (Claude Code, superseded)</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Open-ended code condition</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>0/3 scored correct</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>DeepSeek V4 Pro (Claude Code, superseded)</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Galaxy condition</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>3/3 scored correct</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>DeepSeek V4 Pro (Claude Code, superseded)</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Galaxy condition</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Split (1–2/3)</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>DeepSeek V4 Pro (Claude Code, superseded)</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Galaxy condition</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>0/3 scored correct</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>5</v>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Not scored</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1052,26 +1058,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>benchmark</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>model_configuration</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>execution_condition</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>distinct_answers</t>
-        </is>
-      </c>
       <c r="D1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
         <is>
           <t>replicate_sets</t>
         </is>
@@ -1080,433 +1091,751 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>BixBench-Verified-50</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>GPT-5.5</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Open-ended code condition</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="n">
-        <v>82</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>3/3 scored correct</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>BixBench-Verified-50</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>GPT-5.5</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Open-ended code condition</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" t="n">
-        <v>15</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Split (1–2/3)</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>BixBench-Verified-50</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>GPT-5.5</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Open-ended code condition</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D4" t="n">
-        <v>3</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0/3 scored correct</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>BixBench-Verified-50</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>GPT-5.5</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Galaxy condition</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="n">
-        <v>84</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>3/3 scored correct</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>BixBench-Verified-50</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>GPT-5.5</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Galaxy condition</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" t="n">
-        <v>11</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Split (1–2/3)</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>BixBench-Verified-50</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>GPT-5.5</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Galaxy condition</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D7" t="n">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0/3 scored correct</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>BixBench-Verified-50</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>GPT-5.6 Sol</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Open-ended code condition</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="n">
-        <v>89</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>3/3 scored correct</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>41</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>BixBench-Verified-50</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>GPT-5.6 Sol</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Open-ended code condition</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D9" t="n">
-        <v>10</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Split (1–2/3)</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>BixBench-Verified-50</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>GPT-5.6 Sol</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Open-ended code condition</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>3</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0/3 scored correct</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>BixBench-Verified-50</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>GPT-5.6 Sol</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Galaxy condition</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" t="n">
-        <v>87</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>3/3 scored correct</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>BixBench-Verified-50</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>GPT-5.6 Sol</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Galaxy condition</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Split (1–2/3)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
         <v>2</v>
-      </c>
-      <c r="D12" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>BixBench-Verified-50</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>GPT-5.6 Sol</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Galaxy condition</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>3</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2</v>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0/3 scored correct</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>BixBench-Verified-50</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>GPT-5.6 Luna</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Open-ended code condition</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" t="n">
-        <v>78</v>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3/3 scored correct</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>BixBench-Verified-50</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>GPT-5.6 Luna</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Open-ended code condition</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" t="n">
-        <v>19</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Split (1–2/3)</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>BixBench-Verified-50</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>GPT-5.6 Luna</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Open-ended code condition</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>3</v>
-      </c>
-      <c r="D16" t="n">
-        <v>3</v>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0/3 scored correct</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>BixBench-Verified-50</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>GPT-5.6 Luna</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Galaxy condition</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" t="n">
-        <v>85</v>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>3/3 scored correct</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>BixBench-Verified-50</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>GPT-5.6 Luna</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Galaxy condition</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>2</v>
-      </c>
-      <c r="D18" t="n">
-        <v>9</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Split (1–2/3)</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>BixBench-Verified-50</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>GPT-5.6 Luna</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Galaxy condition</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>3</v>
-      </c>
-      <c r="D19" t="n">
-        <v>6</v>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0/3 scored correct</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>BixBench-Verified-50</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>DeepSeek V4 Pro (Codex)</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Open-ended code condition</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="n">
-        <v>72</v>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>3/3 scored correct</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>BixBench-Verified-50</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>DeepSeek V4 Pro (Codex)</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Open-ended code condition</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>2</v>
-      </c>
-      <c r="D21" t="n">
-        <v>24</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Split (1–2/3)</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>BixBench-Verified-50</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>DeepSeek V4 Pro (Codex)</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Open-ended code condition</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>3</v>
-      </c>
-      <c r="D22" t="n">
-        <v>4</v>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0/3 scored correct</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>BixBench-Verified-50</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>DeepSeek V4 Pro (Codex)</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Galaxy condition</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" t="n">
-        <v>77</v>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>3/3 scored correct</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>BixBench-Verified-50</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>DeepSeek V4 Pro (Codex)</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Galaxy condition</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>2</v>
-      </c>
-      <c r="D24" t="n">
-        <v>15</v>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Split (1–2/3)</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>BixBench-Verified-50</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>DeepSeek V4 Pro (Codex)</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Galaxy condition</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>3</v>
-      </c>
-      <c r="D25" t="n">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>0/3 scored correct</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BixBench-Verified-50</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Claude Code, superseded)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>3/3 scored correct</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BixBench-Verified-50</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Claude Code, superseded)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Split (1–2/3)</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BixBench-Verified-50</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Claude Code, superseded)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>0/3 scored correct</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
         <v>8</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BixBench-Verified-50</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Claude Code, superseded)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>3/3 scored correct</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BixBench-Verified-50</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Claude Code, superseded)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Split (1–2/3)</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BixBench-Verified-50</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Claude Code, superseded)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>0/3 scored correct</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1520,286 +1849,634 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>benchmark</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>model_configuration</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>execution_condition</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>divergence_mechanism</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>scored_incorrect_replicate_runs</t>
-        </is>
-      </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>category</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>replicate_sets</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Open-ended code condition</t>
+          <t>CompBioBench</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Domain convention or definition applied differently</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>11</v>
-      </c>
-      <c r="D2" t="n">
-        <v>45</v>
+          <t>GPT-5.5</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>3/3 matched the consensus answer</t>
+        </is>
       </c>
       <c r="E2" t="n">
-        <v>24.4</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Open-ended code condition</t>
+          <t>CompBioBench</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Error in the final step (sorting, counting, units)</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="n">
-        <v>45</v>
+          <t>GPT-5.5</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Split (1–2/3)</t>
+        </is>
       </c>
       <c r="E3" t="n">
-        <v>2.2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Open-ended code condition</t>
+          <t>CompBioBench</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hand-written method instead of the library method</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>23</v>
-      </c>
-      <c r="D4" t="n">
-        <v>45</v>
+          <t>GPT-5.5</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0/3 matched the consensus answer</t>
+        </is>
       </c>
       <c r="E4" t="n">
-        <v>51.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Open-ended code condition</t>
+          <t>CompBioBench</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Different software version installed</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>7</v>
-      </c>
-      <c r="D5" t="n">
-        <v>45</v>
+          <t>GPT-5.5</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>3/3 matched the consensus answer</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>15.6</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Open-ended code condition</t>
+          <t>CompBioBench</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>No answer submitted</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>45</v>
+          <t>GPT-5.5</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Split (1–2/3)</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Open-ended code condition</t>
+          <t>CompBioBench</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Answer retrieved from benchmark source files</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" t="n">
-        <v>45</v>
+          <t>GPT-5.5</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0/3 matched the consensus answer</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Galaxy condition</t>
+          <t>CompBioBench</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Domain convention or definition applied differently</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>13</v>
-      </c>
-      <c r="D8" t="n">
-        <v>36</v>
+          <t>GPT-5.6 Sol</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>3/3 matched the consensus answer</t>
+        </is>
       </c>
       <c r="E8" t="n">
-        <v>36.1</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Galaxy condition</t>
+          <t>CompBioBench</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Error in the final step (sorting, counting, units)</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>6</v>
-      </c>
-      <c r="D9" t="n">
-        <v>36</v>
+          <t>GPT-5.6 Sol</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Split (1–2/3)</t>
+        </is>
       </c>
       <c r="E9" t="n">
-        <v>16.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Galaxy condition</t>
+          <t>CompBioBench</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hand-written method instead of the library method</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>5</v>
-      </c>
-      <c r="D10" t="n">
-        <v>36</v>
+          <t>GPT-5.6 Sol</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0/3 matched the consensus answer</t>
+        </is>
       </c>
       <c r="E10" t="n">
-        <v>13.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Galaxy condition</t>
+          <t>CompBioBench</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>No answer submitted</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>3</v>
-      </c>
-      <c r="D11" t="n">
-        <v>36</v>
+          <t>GPT-5.6 Sol</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>3/3 matched the consensus answer</t>
+        </is>
       </c>
       <c r="E11" t="n">
-        <v>8.300000000000001</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Galaxy condition</t>
+          <t>CompBioBench</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Galaxy interface trap (silent default, output semantics or job not dispatched)</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>6</v>
-      </c>
-      <c r="D12" t="n">
-        <v>36</v>
+          <t>GPT-5.6 Sol</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Split (1–2/3)</t>
+        </is>
       </c>
       <c r="E12" t="n">
-        <v>16.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Galaxy condition</t>
+          <t>CompBioBench</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Answer retrieved from benchmark source files</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>3</v>
-      </c>
-      <c r="D13" t="n">
-        <v>36</v>
+          <t>GPT-5.6 Sol</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0/3 matched the consensus answer</t>
+        </is>
       </c>
       <c r="E13" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CompBioBench</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GPT-5.6 Luna</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3/3 matched the consensus answer</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CompBioBench</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>GPT-5.6 Luna</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Split (1–2/3)</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CompBioBench</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>GPT-5.6 Luna</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0/3 matched the consensus answer</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CompBioBench</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>GPT-5.6 Luna</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>3/3 matched the consensus answer</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CompBioBench</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>GPT-5.6 Luna</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Split (1–2/3)</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CompBioBench</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>GPT-5.6 Luna</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0/3 matched the consensus answer</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CompBioBench</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Codex)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>3/3 matched the consensus answer</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CompBioBench</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Codex)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Split (1–2/3)</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CompBioBench</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Codex)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0/3 matched the consensus answer</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CompBioBench</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Codex)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>3/3 matched the consensus answer</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CompBioBench</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Codex)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Split (1–2/3)</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CompBioBench</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Codex)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>0/3 matched the consensus answer</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1813,6 +2490,299 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>execution_condition</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>divergence_mechanism</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>scored_incorrect_replicate_runs</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Domain convention or definition applied differently</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D2" t="n">
+        <v>45</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Error in the final step (sorting, counting, units)</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>45</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Hand-written method instead of the library method</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>23</v>
+      </c>
+      <c r="D4" t="n">
+        <v>45</v>
+      </c>
+      <c r="E4" t="n">
+        <v>51.1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Different software version installed</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D5" t="n">
+        <v>45</v>
+      </c>
+      <c r="E5" t="n">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>No answer submitted</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>45</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Answer retrieved from benchmark source files</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>45</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Domain convention or definition applied differently</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>13</v>
+      </c>
+      <c r="D8" t="n">
+        <v>36</v>
+      </c>
+      <c r="E8" t="n">
+        <v>36.1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Error in the final step (sorting, counting, units)</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" t="n">
+        <v>36</v>
+      </c>
+      <c r="E9" t="n">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Hand-written method instead of the library method</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>36</v>
+      </c>
+      <c r="E10" t="n">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>No answer submitted</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>36</v>
+      </c>
+      <c r="E11" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Galaxy interface trap (silent default, output semantics or job not dispatched)</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" t="n">
+        <v>36</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Answer retrieved from benchmark source files</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>36</v>
+      </c>
+      <c r="E13" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
